--- a/media/exports/reports/2025-11/overtime.xlsx
+++ b/media/exports/reports/2025-11/overtime.xlsx
@@ -15,8 +15,8 @@
     <definedName name="Overtime_November">'Report'!$B$8</definedName>
     <definedName name="Overtime_hours_November">'Report'!$B$9</definedName>
     <definedName name="November_last_year">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$19</definedName>
   </definedNames>
@@ -292,12 +292,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$16</f>
+              <f>'Report'!$A$14:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$16</f>
+              <f>'Report'!$B$14:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -399,12 +399,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$28:$A$34</f>
+              <f>'Report'!$A$28:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$28:$B$34</f>
+              <f>'Report'!$B$28:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -473,7 +473,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2610000"/>
+    <ext cx="5400000" cy="2070000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -794,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>October 46.0 h</t>
+          <t>October 38.0 h</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>14.0 h of overtime</t>
+          <t>23.5 h of overtime</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Short-staffed</t>
+          <t>Installation ran over</t>
         </is>
       </c>
       <c r="B15" s="9">
@@ -939,7 +939,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Installation ran over</t>
+          <t>Short-staffed</t>
         </is>
       </c>
       <c r="B16" s="9">
@@ -947,7 +947,17 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Paperwork and quotes</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!B58</f>
+        <v/>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -974,11 +984,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technician T7</t>
+          <t>Technician T5</t>
         </is>
       </c>
       <c r="B28" s="9">
-        <f>Workings!B57</f>
+        <f>Workings!B65</f>
         <v/>
       </c>
     </row>
@@ -989,77 +999,69 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B63</f>
+        <f>Workings!B71</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technician T5</t>
+          <t>Technician T1</t>
         </is>
       </c>
       <c r="B30" s="9">
-        <f>Workings!B69</f>
+        <f>Workings!B77</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technician T3</t>
+          <t>Technician T2</t>
         </is>
       </c>
       <c r="B31" s="9">
-        <f>Workings!B75</f>
+        <f>Workings!B83</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technician T2</t>
+          <t>Technician T3</t>
         </is>
       </c>
       <c r="B32" s="9">
-        <f>Workings!B81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Technician T1</t>
-        </is>
-      </c>
-      <c r="B33" s="9">
-        <f>Workings!B87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Technician T6</t>
-        </is>
-      </c>
-      <c r="B34" s="9">
-        <f>Workings!B93</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="40"/>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Overtime by month: every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
     <row r="41"/>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Overtime by month: every month is on the Data sheet.</t>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Technicians worked 32.0 h of overtime in November, 3.8% of ordinary hours (target under 5.0%), against 3.9% in October. Over the last year it has gone from 2.7% to 3.8%.</t>
         </is>
       </c>
     </row>
@@ -1067,46 +1069,31 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>What it shows</t>
+          <t>What you'd do about it</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Technicians worked 39.5 h of overtime in November, 3.9% of ordinary hours (target under 5.0%), against 4.0% in October. Over the last year it has gone from 1.3% to 3.9%.</t>
+          <t>After-hours call-out is the main reason: 13.5 h, 42.2% of the overtime. Technician T5 carried the most (12.5 h).</t>
         </is>
       </c>
     </row>
     <row r="47"/>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>After-hours call-out is the main reason: 28.5 h, 72.2% of the overtime. Technician T7 carried the most (9.5 h).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
+    <row r="48"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A43:D43"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1125,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1151,7 +1138,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1190,10 +1177,10 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -1203,10 +1190,10 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1003.200000000002</v>
+        <v>851.2000000000016</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>980.400000000002</v>
       </c>
     </row>
     <row r="10">
@@ -1260,10 +1247,10 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -1273,10 +1260,10 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1003.200000000002</v>
+        <v>851.2000000000016</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>980.400000000002</v>
       </c>
     </row>
     <row r="18">
@@ -1325,7 +1312,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="25">
@@ -1335,7 +1322,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1094.400000000001</v>
+        <v>866.4000000000017</v>
       </c>
     </row>
     <row r="26">
@@ -1387,7 +1374,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="34">
@@ -1397,7 +1384,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1416,7 +1403,7 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Short-staffed: overtime, November 2025</t>
+          <t>Installation ran over: overtime, November 2025</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1429,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="42">
@@ -1452,7 +1439,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -1471,7 +1458,7 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Installation ran over: overtime, November 2025</t>
+          <t>Short-staffed: overtime, November 2025</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1494,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -1526,14 +1513,14 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Technician T7: overtime, November 2025</t>
+          <t>Paperwork and quotes: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Overtime hours on this technician's shifts</t>
+          <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
@@ -1546,238 +1533,224 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="B57" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>All overtime hours</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="B59" s="15">
+        <f>B57/B58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Technician T5: overtime, November 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Overtime hours on this technician's shifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>Technician T4: overtime, November 2025</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr"/>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B63" s="16" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>Technician T5: overtime, November 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="B71" s="16" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Technician T1: overtime, November 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr"/>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="B77" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Technician T2: overtime, November 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Overtime hours on this technician's shifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr"/>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
         <is>
           <t>Technician T3: overtime, November 2025</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr"/>
-      <c r="B74" s="5" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr"/>
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B75" s="16" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>Technician T2: overtime, November 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Overtime hours on this technician's shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr"/>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>Overtime hours</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>Technician T1: overtime, November 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Overtime hours on this technician's shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr"/>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
-        <is>
-          <t>Overtime hours</t>
-        </is>
-      </c>
-      <c r="B87" s="16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>Technician T6: overtime, November 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Overtime hours on this technician's shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr"/>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
-        <is>
-          <t>Overtime hours</t>
-        </is>
-      </c>
-      <c r="B93" s="16" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
+      <c r="B89" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
+  <rowBreaks count="2" manualBreakCount="2">
     <brk id="29" min="0" max="16383" man="1"/>
-    <brk id="59" min="0" max="16383" man="1"/>
-    <brk id="89" min="0" max="16383" man="1"/>
+    <brk id="61" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1815,7 +1788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1859,10 +1832,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1132.400000000001</v>
+        <v>957.600000000002</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="E6" s="18">
         <f>IF(C6=0,"",D6/C6)</f>
@@ -1881,10 +1854,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1094.400000000001</v>
+        <v>866.4000000000017</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="E7" s="18">
         <f>IF(C7=0,"",D7/C7)</f>
@@ -1903,10 +1876,10 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1010.800000000002</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="E8" s="18">
         <f>IF(C8=0,"",D8/C8)</f>
@@ -1925,10 +1898,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1086.800000000001</v>
+        <v>904.4000000000018</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="E9" s="18">
         <f>IF(C9=0,"",D9/C9)</f>
@@ -1947,10 +1920,10 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>995.6000000000021</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>28</v>
+        <v>41.5</v>
       </c>
       <c r="E10" s="18">
         <f>IF(C10=0,"",D10/C10)</f>
@@ -1969,10 +1942,10 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1079.200000000001</v>
+        <v>912.0000000000018</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>26</v>
+        <v>40.5</v>
       </c>
       <c r="E11" s="18">
         <f>IF(C11=0,"",D11/C11)</f>
@@ -1991,10 +1964,10 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>950.0000000000019</v>
+        <v>836.0000000000016</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>34.5</v>
+        <v>30.5</v>
       </c>
       <c r="E12" s="18">
         <f>IF(C12=0,"",D12/C12)</f>
@@ -2013,10 +1986,10 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1086.800000000001</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" s="18">
         <f>IF(C13=0,"",D13/C13)</f>
@@ -2035,10 +2008,10 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1079.200000000001</v>
+        <v>942.4000000000019</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="E14" s="18">
         <f>IF(C14=0,"",D14/C14)</f>
@@ -2057,10 +2030,10 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1140.000000000001</v>
+        <v>1033.600000000002</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>27.5</v>
+        <v>34.5</v>
       </c>
       <c r="E15" s="18">
         <f>IF(C15=0,"",D15/C15)</f>
@@ -2079,10 +2052,10 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1048.800000000002</v>
+        <v>874.0000000000017</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>48.5</v>
+        <v>28.5</v>
       </c>
       <c r="E16" s="18">
         <f>IF(C16=0,"",D16/C16)</f>
@@ -2101,10 +2074,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1117.200000000001</v>
+        <v>957.600000000002</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>34</v>
+        <v>35.5</v>
       </c>
       <c r="E17" s="18">
         <f>IF(C17=0,"",D17/C17)</f>
@@ -2123,10 +2096,10 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>980.400000000002</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E18" s="18">
         <f>IF(C18=0,"",D18/C18)</f>
@@ -2145,10 +2118,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1003.200000000002</v>
+        <v>851.2000000000016</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
       <c r="E19" s="18">
         <f>IF(C19=0,"",D19/C19)</f>
@@ -2161,7 +2134,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-11/overtime.xlsx
+++ b/media/exports/reports/2025-11/overtime.xlsx
@@ -12,10 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Overtime_November">'Report'!$B$8</definedName>
-    <definedName name="Overtime_hours_November">'Report'!$B$9</definedName>
-    <definedName name="November_last_year">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$46</definedName>
+    <definedName name="Overtime_November">'Report'!$B$9</definedName>
+    <definedName name="Overtime_hours_November">'Report'!$B$10</definedName>
+    <definedName name="November_last_year">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$19</definedName>
@@ -54,6 +54,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -74,11 +79,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -116,36 +116,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -292,12 +295,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$17</f>
+              <f>'Report'!$A$15:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$17</f>
+              <f>'Report'!$B$15:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -399,12 +402,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$28:$A$32</f>
+              <f>'Report'!$A$29:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$28:$B$32</f>
+              <f>'Report'!$B$29:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -448,7 +451,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="1980000"/>
@@ -470,7 +473,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2070000"/>
@@ -794,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -820,7 +823,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -828,137 +831,143 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Overtime was 3.8% of ordinary hours in November (target under 5.0%), up from 2.7% a year earlier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Each technician's paid hours, day by day: ordinary hours and overtime, with the main reason for the overtime.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Overtime, November</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>of ordinary hours · target under 5.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Overtime hours, November</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B18</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>October 38.0 h</t>
+          <t>Overtime, November</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>of ordinary hours · target under 5.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Overtime hours, November</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>Workings!B16</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>October 38.0 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>November last year</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="7">
         <f>Workings!B26</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>23.5 h of overtime</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Why the overtime, November 2025</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Why the overtime</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>After-hours call-out</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>Workings!B34</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Installation ran over</t>
+          <t>After-hours call-out</t>
         </is>
       </c>
       <c r="B15" s="9">
-        <f>Workings!B42</f>
+        <f>Workings!B33</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Short-staffed</t>
+          <t>Installation ran over</t>
         </is>
       </c>
       <c r="B16" s="9">
-        <f>Workings!B50</f>
+        <f>Workings!B41</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Short-staffed</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Paperwork and quotes</t>
         </is>
       </c>
-      <c r="B17" s="9">
-        <f>Workings!B58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="B18" s="9">
+        <f>Workings!B57</f>
+        <v/>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -966,141 +975,143 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Overtime by technician, November 2025</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Overtime by technician</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Technician T5</t>
-        </is>
-      </c>
-      <c r="B28" s="9">
-        <f>Workings!B65</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technician T4</t>
+          <t>Technician T5</t>
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B71</f>
+        <f>Workings!B65</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technician T1</t>
+          <t>Technician T4</t>
         </is>
       </c>
       <c r="B30" s="9">
-        <f>Workings!B77</f>
+        <f>Workings!B71</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technician T2</t>
+          <t>Technician T1</t>
         </is>
       </c>
       <c r="B31" s="9">
-        <f>Workings!B83</f>
+        <f>Workings!B77</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Technician T2</t>
+        </is>
+      </c>
+      <c r="B32" s="9">
+        <f>Workings!B83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Technician T3</t>
         </is>
       </c>
-      <c r="B32" s="9">
+      <c r="B33" s="9">
         <f>Workings!B89</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Overtime by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Technicians worked 32.0 h of overtime in November, 3.8% of ordinary hours (target under 5.0%), against 3.9% in October. Over the last year it has gone from 2.7% to 3.8%.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>After-hours call-out is the main reason: 13.5 h, 42.2% of the overtime. Technician T5 carried the most (12.5 h).</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48"/>
+    <row r="49"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="26" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1138,33 +1149,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Overtime, November and October</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
@@ -1176,10 +1187,10 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1189,24 +1200,24 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>851.2000000000016</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>980.400000000002</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <f>C8/C9</f>
         <v/>
       </c>
@@ -1214,27 +1225,27 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Overtime, November and October</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
@@ -1246,10 +1257,10 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1259,24 +1270,24 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>851.2000000000016</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>980.400000000002</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <f>B16/B17</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <f>C16/C17</f>
         <v/>
       </c>
@@ -1284,22 +1295,22 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Overtime, Nov 24</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
@@ -1311,7 +1322,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>23.5</v>
       </c>
     </row>
@@ -1321,17 +1332,17 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>866.4000000000017</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Overtime as a share of ordinary hours</t>
         </is>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="16">
         <f>B24/B25</f>
         <v/>
       </c>
@@ -1346,22 +1357,22 @@
     <row r="28"/>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>After-hours call-out: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1373,7 +1384,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="14" t="n">
         <v>13.5</v>
       </c>
     </row>
@@ -1383,17 +1394,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <f>B33/B34</f>
         <v/>
       </c>
@@ -1401,22 +1412,22 @@
     <row r="36"/>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Installation ran over: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1428,7 +1439,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="14" t="n">
         <v>11.5</v>
       </c>
     </row>
@@ -1438,17 +1449,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="14" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="16">
         <f>B41/B42</f>
         <v/>
       </c>
@@ -1456,22 +1467,22 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Short-staffed: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr"/>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1483,7 +1494,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n">
+      <c r="B49" s="14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1493,17 +1504,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="B50" s="14" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="16">
         <f>B49/B50</f>
         <v/>
       </c>
@@ -1511,22 +1522,22 @@
     <row r="52"/>
     <row r="53"/>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Paperwork and quotes: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr"/>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1538,7 +1549,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
+      <c r="B57" s="14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1548,17 +1559,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n">
+      <c r="B58" s="14" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="16">
         <f>B57/B58</f>
         <v/>
       </c>
@@ -1566,170 +1577,170 @@
     <row r="60"/>
     <row r="61"/>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Technician T5: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr"/>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n">
+      <c r="B65" s="17" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="66"/>
     <row r="67"/>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>Technician T4: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B71" s="16" t="n">
+      <c r="B71" s="17" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73"/>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Technician T1: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr"/>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="14" t="inlineStr">
+      <c r="A77" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n">
+      <c r="B77" s="17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="78"/>
     <row r="79"/>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Technician T2: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr"/>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B83" s="16" t="n">
+      <c r="B83" s="17" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="84"/>
     <row r="85"/>
     <row r="86">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Technician T3: overtime, November 2025</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr"/>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="14" t="inlineStr">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B89" s="16" t="n">
+      <c r="B89" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1742,7 +1753,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1788,342 +1799,342 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Overtime share</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>957.600000000002</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>15.5</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>IF(C6=0,"",D6/C6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>866.4000000000017</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>23.5</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>IF(C7=0,"",D7/C7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>19.5</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>IF(C8=0,"",D8/C8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>904.4000000000018</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>27.5</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>IF(C9=0,"",D9/C9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>41.5</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>IF(C10=0,"",D10/C10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>912.0000000000018</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>40.5</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>IF(C11=0,"",D11/C11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>836.0000000000016</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>30.5</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>IF(C12=0,"",D12/C12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IF(C13=0,"",D13/C13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>942.4000000000019</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>26.5</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IF(C14=0,"",D14/C14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>1033.600000000002</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>34.5</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IF(C15=0,"",D15/C15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>874.0000000000017</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>28.5</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>IF(C16=0,"",D16/C16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>957.600000000002</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>35.5</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="19">
         <f>IF(C17=0,"",D17/C17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>980.400000000002</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <f>IF(C18=0,"",D18/C18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>851.2000000000016</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="19">
         <f>IF(C19=0,"",D19/C19)</f>
         <v/>
       </c>
@@ -2134,7 +2145,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
